--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,302 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129964212</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97665</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>633756</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6659871</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129964214</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>633748</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6659833</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3 buketter</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129964208</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>633752</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6659861</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129964212</v>
       </c>
       <c r="B3" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129964214</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129964208</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129964212</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129964214</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129964208</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129964212</v>
       </c>
       <c r="B3" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129964214</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129964208</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129964212</v>
       </c>
       <c r="B3" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129964214</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129964208</v>
       </c>
       <c r="B5" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,7 +807,7 @@
         <v>129964212</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129964214</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>129964208</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,6 +1097,704 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130267692</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91749</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633636</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6659716</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130267696</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633759</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6659844</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130267722</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633664</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6659629</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130267707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633755</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6659861</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130267697</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>633702</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6659833</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130267690</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>633754</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6659849</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130267711</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633765</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6659839</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 1213</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130267692</v>
       </c>
       <c r="B6" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,45 +1298,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267722</v>
+        <v>130267707</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633664</v>
+        <v>633755</v>
       </c>
       <c r="R8" t="n">
-        <v>6659629</v>
+        <v>6659861</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,12 +1375,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,49 +1405,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267707</v>
+        <v>130267722</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633755</v>
+        <v>633664</v>
       </c>
       <c r="R9" t="n">
-        <v>6659861</v>
+        <v>6659629</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1472,18 +1478,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267697</v>
+        <v>130267690</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633702</v>
+        <v>633754</v>
       </c>
       <c r="R10" t="n">
-        <v>6659833</v>
+        <v>6659849</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267690</v>
+        <v>130267697</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633754</v>
+        <v>633702</v>
       </c>
       <c r="R11" t="n">
-        <v>6659849</v>
+        <v>6659833</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130267692</v>
       </c>
       <c r="B6" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>130267696</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,49 +1298,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267707</v>
+        <v>130267722</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633755</v>
+        <v>633664</v>
       </c>
       <c r="R8" t="n">
-        <v>6659861</v>
+        <v>6659629</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,18 +1371,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,45 +1395,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267722</v>
+        <v>130267707</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633664</v>
+        <v>633755</v>
       </c>
       <c r="R9" t="n">
-        <v>6659629</v>
+        <v>6659861</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,12 +1472,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>130267690</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>130267697</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267690</v>
+        <v>130267697</v>
       </c>
       <c r="B10" t="n">
-        <v>58011</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633754</v>
+        <v>633702</v>
       </c>
       <c r="R10" t="n">
-        <v>6659849</v>
+        <v>6659833</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267697</v>
+        <v>130267690</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>58011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633702</v>
+        <v>633754</v>
       </c>
       <c r="R11" t="n">
-        <v>6659833</v>
+        <v>6659849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130267692</v>
       </c>
       <c r="B6" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,45 +1298,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267722</v>
+        <v>130267707</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633664</v>
+        <v>633755</v>
       </c>
       <c r="R8" t="n">
-        <v>6659629</v>
+        <v>6659861</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,12 +1375,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,49 +1405,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267707</v>
+        <v>130267722</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633755</v>
+        <v>633664</v>
       </c>
       <c r="R9" t="n">
-        <v>6659861</v>
+        <v>6659629</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1472,18 +1478,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267697</v>
+        <v>130267690</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>58011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633702</v>
+        <v>633754</v>
       </c>
       <c r="R10" t="n">
-        <v>6659833</v>
+        <v>6659849</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267690</v>
+        <v>130267697</v>
       </c>
       <c r="B11" t="n">
-        <v>58011</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633754</v>
+        <v>633702</v>
       </c>
       <c r="R11" t="n">
-        <v>6659849</v>
+        <v>6659833</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130267692</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,49 +1298,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267707</v>
+        <v>130267722</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633755</v>
+        <v>633664</v>
       </c>
       <c r="R8" t="n">
-        <v>6659861</v>
+        <v>6659629</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,18 +1371,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,45 +1395,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267722</v>
+        <v>130267707</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>98951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633664</v>
+        <v>633755</v>
       </c>
       <c r="R9" t="n">
-        <v>6659629</v>
+        <v>6659861</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,12 +1472,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267690</v>
+        <v>130267697</v>
       </c>
       <c r="B10" t="n">
-        <v>58011</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633754</v>
+        <v>633702</v>
       </c>
       <c r="R10" t="n">
-        <v>6659849</v>
+        <v>6659833</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267697</v>
+        <v>130267690</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>58011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633702</v>
+        <v>633754</v>
       </c>
       <c r="R11" t="n">
-        <v>6659833</v>
+        <v>6659849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130267692</v>
       </c>
       <c r="B6" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>130267696</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>130267707</v>
       </c>
       <c r="B9" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>130267697</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>130267690</v>
       </c>
       <c r="B11" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1298,45 +1298,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267722</v>
+        <v>130267707</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>98957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633664</v>
+        <v>633755</v>
       </c>
       <c r="R8" t="n">
-        <v>6659629</v>
+        <v>6659861</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1371,12 +1375,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,49 +1405,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267707</v>
+        <v>130267722</v>
       </c>
       <c r="B9" t="n">
-        <v>98953</v>
+        <v>8440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633755</v>
+        <v>633664</v>
       </c>
       <c r="R9" t="n">
-        <v>6659861</v>
+        <v>6659629</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1472,18 +1478,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1298,49 +1298,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267707</v>
+        <v>130267722</v>
       </c>
       <c r="B8" t="n">
-        <v>98957</v>
+        <v>8440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633755</v>
+        <v>633664</v>
       </c>
       <c r="R8" t="n">
-        <v>6659861</v>
+        <v>6659629</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,18 +1371,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,45 +1395,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267722</v>
+        <v>130267707</v>
       </c>
       <c r="B9" t="n">
-        <v>8440</v>
+        <v>98957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633664</v>
+        <v>633755</v>
       </c>
       <c r="R9" t="n">
-        <v>6659629</v>
+        <v>6659861</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,12 +1472,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130267692</v>
       </c>
       <c r="B6" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>130267696</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>130267707</v>
       </c>
       <c r="B9" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267697</v>
+        <v>130267690</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633702</v>
+        <v>633754</v>
       </c>
       <c r="R10" t="n">
-        <v>6659833</v>
+        <v>6659849</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267690</v>
+        <v>130267697</v>
       </c>
       <c r="B11" t="n">
-        <v>58013</v>
+        <v>57859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633754</v>
+        <v>633702</v>
       </c>
       <c r="R11" t="n">
-        <v>6659849</v>
+        <v>6659833</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,7 +1699,7 @@
         <v>130267711</v>
       </c>
       <c r="B12" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122965679</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122965679</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59539-2025 artfynd.xlsx
+++ b/artfynd/A 59539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122965679</v>
+        <v>129964208</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633748</v>
+        <v>633752</v>
       </c>
       <c r="R2" t="n">
-        <v>6659611</v>
+        <v>6659861</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,53 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Mosse med tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129964212</v>
+        <v>130267686</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633756</v>
+        <v>633792</v>
       </c>
       <c r="R3" t="n">
-        <v>6659871</v>
+        <v>6659858</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129964214</v>
+        <v>130267687</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633748</v>
+        <v>633708</v>
       </c>
       <c r="R4" t="n">
-        <v>6659833</v>
+        <v>6659850</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -961,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 buketter</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129964208</v>
+        <v>130267692</v>
       </c>
       <c r="B5" t="n">
-        <v>91728</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633752</v>
+        <v>633636</v>
       </c>
       <c r="R5" t="n">
-        <v>6659861</v>
+        <v>6659716</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,12 +1034,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,48 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267692</v>
+        <v>130267682</v>
       </c>
       <c r="B6" t="n">
-        <v>91795</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633636</v>
+        <v>633707</v>
       </c>
       <c r="R6" t="n">
-        <v>6659716</v>
+        <v>6659848</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1171,13 +1140,17 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,14 +1169,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267696</v>
+        <v>130267695</v>
       </c>
       <c r="B7" t="n">
-        <v>57859</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1231,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633759</v>
+        <v>633782</v>
       </c>
       <c r="R7" t="n">
-        <v>6659844</v>
+        <v>6659835</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1293,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267722</v>
+        <v>130267696</v>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633664</v>
+        <v>633759</v>
       </c>
       <c r="R8" t="n">
-        <v>6659629</v>
+        <v>6659844</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1390,49 +1363,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267707</v>
+        <v>130267697</v>
       </c>
       <c r="B9" t="n">
-        <v>98970</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633755</v>
+        <v>633702</v>
       </c>
       <c r="R9" t="n">
-        <v>6659861</v>
+        <v>6659833</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1467,18 +1436,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5 buketter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1497,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267690</v>
+        <v>122965679</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,20 +1488,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633754</v>
+        <v>633748</v>
       </c>
       <c r="R10" t="n">
-        <v>6659849</v>
+        <v>6659611</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1562,12 +1537,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,26 +1563,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130267697</v>
+        <v>130267690</v>
       </c>
       <c r="B11" t="n">
-        <v>57859</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633702</v>
+        <v>633754</v>
       </c>
       <c r="R11" t="n">
-        <v>6659833</v>
+        <v>6659849</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1691,32 +1681,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130267711</v>
+        <v>130267678</v>
       </c>
       <c r="B12" t="n">
-        <v>98970</v>
+        <v>5199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633765</v>
+        <v>633792</v>
       </c>
       <c r="R12" t="n">
-        <v>6659839</v>
+        <v>6659859</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1764,11 +1754,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10 1213</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1790,6 +1775,716 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130267722</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>633664</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6659629</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129964214</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633748</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6659833</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 buketter</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130267707</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>633755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6659861</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 buketter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130267708</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>633708</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6659850</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4 buketter</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130267711</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>633765</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6659839</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10 1213</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129964213</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>633783</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6659870</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129964212</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Enbärsmossarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>633756</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6659871</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
